--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -741,20 +732,20 @@
       <c r="D4" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H4" s="8" t="n">
-        <v>10.8</v>
+      <c r="H4" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
@@ -762,23 +753,23 @@
       <c r="K4" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="3" t="n">
         <v>16</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>19.7</v>
+        <v>17.7</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>17.3</v>
@@ -792,7 +783,7 @@
       <c r="U4" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V4" s="8" t="n">
+      <c r="V4" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="W4" s="3" t="n">
@@ -805,7 +796,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>9.5</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -835,7 +826,7 @@
       <c r="G5" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
@@ -857,19 +848,19 @@
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>98.8</v>
+        <v>98</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>81</v>
@@ -880,7 +871,7 @@
       <c r="V5" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -890,7 +881,7 @@
         <v>76</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -914,13 +905,13 @@
       <c r="E6" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H6" s="8" t="n">
+      <c r="G6" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
@@ -930,13 +921,13 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>94.2</v>
+      <c r="M6" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>16.1</v>
@@ -955,7 +946,7 @@
         <v>12.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>62.5</v>
+        <v>67.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
@@ -967,7 +958,7 @@
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>29</v>
+        <v>20.2</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>76</v>
@@ -1025,16 +1016,16 @@
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.8</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>12.2</v>
+        <v>17.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>18</v>
@@ -1045,20 +1036,20 @@
       <c r="U7" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>15.3</v>
+        <v>18.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>8.4</v>
+        <v>84</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>33.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1082,11 +1073,11 @@
       <c r="E8" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>14.2</v>
@@ -1095,7 +1086,7 @@
         <v>0.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
@@ -1103,20 +1094,20 @@
       <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>13.1</v>
+      <c r="M8" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>17.1</v>
+        <v>171.9</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>9.9</v>
+        <v>99</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>22.7</v>
+        <v>22.1</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>18.6</v>
@@ -1125,7 +1116,7 @@
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>7.2</v>
@@ -1159,7 +1150,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>182.5</v>
+        <v>1825.2</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>126.5</v>
@@ -1180,7 +1171,7 @@
         <v>6.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>91.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>28.9</v>
@@ -1192,10 +1183,10 @@
         <v>74.3</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>95.3</v>
+        <v>493</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.4</v>
@@ -1207,16 +1198,16 @@
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>198.6</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>891.8</v>
+        <v>2.8</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>95.3</v>
+        <v>95.5</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>87.2</v>
@@ -1225,7 +1216,7 @@
         <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9429</v>
+        <v>429</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>16.1</v>
@@ -1265,10 +1256,10 @@
         <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.1</v>
+        <v>10.1</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>15</v>
@@ -1280,7 +1271,7 @@
         <v>16.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>28.6</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.3</v>
@@ -1300,8 +1291,8 @@
       <c r="U10" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="V10" s="8" t="n">
-        <v>191.4</v>
+      <c r="V10" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>17.4</v>
@@ -1310,7 +1301,7 @@
         <v>19</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>88.8</v>
+        <v>86.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>3.2</v>
@@ -1335,10 +1326,10 @@
         <v>23.4</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>55.3</v>
+        <v>13.3</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
@@ -1352,17 +1343,17 @@
       <c r="J11" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K11" s="8" t="n">
+      <c r="K11" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="L11" s="8" t="n">
-        <v>122.8</v>
+      <c r="L11" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>99</v>
@@ -1370,35 +1361,35 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="8" t="n">
-        <v>2.3</v>
+      <c r="Q11" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>29.3</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1220.4</v>
+        <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>158.6</v>
-      </c>
-      <c r="W11" s="8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W11" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>18.9</v>
+        <v>16.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>93.8</v>
+        <v>95</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1432,28 +1423,28 @@
         <v>10</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L12" s="8" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>24.4</v>
+      <c r="L12" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.9</v>
+        <v>16.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>24.3</v>
@@ -1465,7 +1456,7 @@
         <v>16.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
@@ -1473,17 +1464,17 @@
       <c r="V12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W12" s="8" t="n">
+      <c r="W12" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>281</v>
+        <v>85</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1504,7 +1495,7 @@
       <c r="D13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="F13" s="3" t="n">
@@ -1517,7 +1508,7 @@
         <v>8.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.8</v>
@@ -1526,19 +1517,19 @@
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>98.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
@@ -1550,7 +1541,7 @@
         <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>1866.8</v>
+        <v>66.8</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1565,7 +1556,7 @@
         <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>726</v>
+        <v>26</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6</v>
@@ -1584,7 +1575,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>331.9</v>
+        <v>531.1</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>26.8</v>
@@ -1592,7 +1583,7 @@
       <c r="E14" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1602,7 +1593,7 @@
         <v>8.9</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>3.6</v>
@@ -1614,16 +1605,16 @@
         <v>12.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.6</v>
@@ -1647,10 +1638,10 @@
         <v>18.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>29.3</v>
+        <v>20.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>8.4</v>
+        <v>84</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>4</v>
@@ -1675,22 +1666,22 @@
         <v>26.7</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>22.6</v>
+        <v>12.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>10.9</v>
+        <v>21.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>1.6</v>
@@ -1698,14 +1689,14 @@
       <c r="L15" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M15" s="8" t="n">
-        <v>14.9</v>
+      <c r="M15" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
@@ -1735,7 +1726,7 @@
         <v>18.6</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>84.8</v>
+        <v>84</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>3.6</v>
@@ -1754,7 +1745,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2306.9</v>
+        <v>230.6</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>127.2</v>
@@ -1766,7 +1757,7 @@
         <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>48.9</v>
@@ -1775,7 +1766,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>19.6</v>
@@ -1790,14 +1781,14 @@
         <v>45.6</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>432</v>
+        <v>493</v>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="3" t="n">
-        <v>115.7</v>
+        <v>118.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>91.59999999999999</v>
@@ -1806,22 +1797,22 @@
         <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>255.8</v>
+        <v>55.8</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>100.4</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>190.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>921</v>
+        <v>424</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>118.4</v>
+        <v>18.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1845,11 +1836,11 @@
       <c r="E17" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="G17" s="8" t="n">
-        <v>112.4</v>
+      <c r="G17" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1860,11 +1851,11 @@
       <c r="J17" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="K17" s="8" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>13.9</v>
+      <c r="K17" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>13.2</v>
@@ -1890,11 +1881,11 @@
       <c r="T17" s="3" t="n">
         <v>62.6</v>
       </c>
-      <c r="U17" s="8" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>1.4</v>
+      <c r="U17" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>18.2</v>
@@ -1924,13 +1915,13 @@
       <c r="C18" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E18" s="8" t="n">
+      <c r="D18" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1949,34 +1940,34 @@
         <v>0.3</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.2</v>
+        <v>14.2</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>14</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q18" s="8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="R18" s="8" t="n">
+      <c r="Q18" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R18" s="3" t="n">
         <v>19</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>20.2</v>
@@ -2007,40 +1998,40 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>435.6</v>
+        <v>2135.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="M19" s="8" t="n">
-        <v>11.8</v>
+      <c r="M19" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>12.6</v>
+        <v>18.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>47</v>
@@ -2049,13 +2040,13 @@
         <v>0.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="8" t="n">
-        <v>79.40000000000001</v>
+      <c r="S19" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>36.1</v>
@@ -2063,7 +2054,7 @@
       <c r="U19" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V19" s="8" t="n">
+      <c r="V19" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2092,15 +2083,15 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1417.9</v>
+        <v>417.9</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>125.4</v>
-      </c>
-      <c r="F20" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="G20" s="3" t="n">
@@ -2125,7 +2116,7 @@
         <v>12.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>184.4</v>
@@ -2134,7 +2125,7 @@
         <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>13.4</v>
+        <v>23.4</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>17.5</v>
@@ -2143,13 +2134,13 @@
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>12.2</v>
+        <v>19.2</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>17.7</v>
@@ -2158,7 +2149,7 @@
         <v>19.4</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>2.9</v>
@@ -2177,15 +2168,15 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>379.3</v>
+        <v>371.3</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E21" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2198,10 +2189,10 @@
         <v>1.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>41.1</v>
+        <v>2.1</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>16.5</v>
@@ -2210,13 +2201,13 @@
         <v>16.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
@@ -2236,17 +2227,17 @@
       <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="W21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>918.1</v>
+        <v>98</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2267,10 +2258,10 @@
       <c r="D22" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="E22" s="8" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="F22" s="8" t="n">
+      <c r="E22" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F22" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2286,19 +2277,19 @@
         <v>3.5</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>51.7</v>
+        <v>5.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>1.3</v>
+        <v>13.2</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.4</v>
+        <v>14.4</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>297</v>
+        <v>97</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.6</v>
@@ -2310,13 +2301,13 @@
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>59.8</v>
+        <v>59</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>18.2</v>
+        <v>1.2</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>18.9</v>
@@ -2368,13 +2359,13 @@
         <v>1.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.9</v>
+        <v>15.4</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>27.4</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>80.7</v>
+        <v>70.7</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>69.59999999999999</v>
@@ -2386,20 +2377,20 @@
         <v>489</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>19.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>115.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>191.5</v>
+        <v>91.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>232.8</v>
+        <v>328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>149.8</v>
+        <v>49.8</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>94.3</v>
@@ -2411,10 +2402,10 @@
         <v>93</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>429.8</v>
+        <v>429</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2432,36 +2423,38 @@
       <c r="C24" s="3" t="n">
         <v>417.9</v>
       </c>
-      <c r="D24" s="8" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E24" s="8" t="n">
+      <c r="D24" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E24" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="H24" s="8" t="n">
+      <c r="G24" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>3.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="M24" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="M24" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.7</v>
+        <v>26.2</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
@@ -2479,12 +2472,12 @@
         <v>18.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>15.4</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="8" t="n">
+      <c r="V24" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="W24" s="3" t="n">
@@ -2497,7 +2490,7 @@
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2519,7 +2512,7 @@
         <v>23.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>13.3</v>
+        <v>15.5</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>19.3</v>
@@ -2527,7 +2520,7 @@
       <c r="G25" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="H25" s="8" t="n">
+      <c r="H25" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
@@ -2537,16 +2530,16 @@
         <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L25" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L25" s="3" t="n">
         <v>16</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>98</v>
@@ -2555,7 +2548,7 @@
         <v>0.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>17.2</v>
@@ -2569,8 +2562,8 @@
       <c r="U25" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="V25" s="8" t="n">
-        <v>27.9</v>
+      <c r="V25" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>17</v>
@@ -2579,7 +2572,7 @@
         <v>3.4</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>1</v>
@@ -2598,7 +2591,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>228.3</v>
+        <v>268.3</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>22.4</v>
@@ -2610,10 +2603,10 @@
         <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>7.1</v>
+        <v>71.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.7</v>
@@ -2627,29 +2620,29 @@
       <c r="L26" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>18.2</v>
+        <v>12.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="S26" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S26" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>1.6</v>
@@ -2690,14 +2683,14 @@
       <c r="F27" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G27" s="8" t="n">
-        <v>12.2</v>
+      <c r="G27" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
@@ -2705,14 +2698,14 @@
       <c r="K27" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="L27" s="8" t="n">
-        <v>73.5</v>
+      <c r="L27" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>15.4</v>
+        <v>13.4</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>99</v>
@@ -2727,22 +2720,22 @@
         <v>18.8</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>28.1</v>
+        <v>20.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="8" t="n">
+      <c r="V27" s="3" t="n">
         <v>19</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>88</v>
@@ -2785,7 +2778,7 @@
         <v>0.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>32.8</v>
@@ -2797,10 +2790,10 @@
         <v>14.3</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>16.2</v>
+        <v>12.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.4</v>
@@ -2808,22 +2801,22 @@
       <c r="Q28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>11.9</v>
+        <v>16.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>48.1</v>
+        <v>18</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2849,10 +2842,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>309.7</v>
+        <v>309.1</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>14</v>
@@ -2863,7 +2856,7 @@
       <c r="G29" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="I29" s="3" t="n">
@@ -2873,19 +2866,19 @@
         <v>1.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M29" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M29" s="3" t="n">
         <v>15</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0.2</v>
@@ -2893,29 +2886,29 @@
       <c r="Q29" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>19</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>1.1</v>
+        <v>19.1</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>6.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V29" s="8" t="n">
-        <v>35.8</v>
+      <c r="V29" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X29" s="8" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X29" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>0.6</v>
@@ -2934,10 +2927,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>15.6</v>
+        <v>156.9</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>116.8</v>
+        <v>1168.2</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>71.90000000000001</v>
@@ -2967,14 +2960,14 @@
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>494.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>89.2</v>
@@ -2989,7 +2982,7 @@
         <v>21.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>8.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>82.40000000000001</v>
@@ -2998,10 +2991,10 @@
         <v>92.09999999999999</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>9428</v>
+        <v>478</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3019,14 +3012,14 @@
       <c r="C31" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="D31" s="8" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E31" s="8" t="n">
+      <c r="D31" s="3" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="F31" s="8" t="n">
-        <v>18.9</v>
+      <c r="F31" s="3" t="n">
+        <v>118.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>90.40000000000001</v>
@@ -3041,38 +3034,38 @@
         <v>0.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="8" t="n">
-        <v>14.9</v>
+      <c r="M31" s="3" t="n">
+        <v>149.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>60.4</v>
+        <v>22.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.1</v>
+        <v>20.1</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>87.8</v>
+      <c r="R31" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.1</v>
+        <v>14.4</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>17</v>
+        <v>170.4</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>16.3</v>
@@ -3084,7 +3077,7 @@
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3100,72 +3093,72 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>364.2</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>81.90000000000001</v>
+        <v>364.6</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1815</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>32.3</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>1.1</v>
+        <v>21.9</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="R32" s="8" t="n">
-        <v>19.5</v>
+      <c r="R32" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="8" t="n">
+      <c r="V32" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>1.2</v>
+        <v>12.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>8.6</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3186,16 +3179,16 @@
       <c r="D33" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>81.7</v>
+      <c r="F33" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H33" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="I33" s="3" t="n">
@@ -3208,13 +3201,13 @@
         <v>7.2</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="N33" s="8" t="n">
-        <v>9161.9</v>
+      <c r="N33" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3229,28 +3222,28 @@
         <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>71.8</v>
+        <v>77.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>2880.9</v>
+        <v>88</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3278,7 +3271,7 @@
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>14.2</v>
@@ -3290,52 +3283,52 @@
         <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>5.1</v>
+        <v>1150</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>29.1</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>97.5</v>
+        <v>17.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="W34" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W34" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3354,12 +3347,12 @@
         <v>477.8</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>14.2</v>
+        <v>24.2</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3380,7 +3373,7 @@
       <c r="L35" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3392,25 +3385,25 @@
       <c r="P35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q35" s="8" t="n">
+      <c r="Q35" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>11.9</v>
+        <v>27.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>60.8</v>
+        <v>60</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="W35" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="W35" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3420,7 +3413,7 @@
         <v>84</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>128.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3441,7 +3434,7 @@
       <c r="D36" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="E36" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F36" s="3" t="n">
@@ -3451,7 +3444,7 @@
         <v>11.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>3.3</v>
@@ -3472,13 +3465,13 @@
         <v>16.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
-        <v>21</v>
+      <c r="Q36" s="3" t="n">
+        <v>24</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.6</v>
@@ -3487,10 +3480,10 @@
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>32.1</v>
+        <v>54.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.8</v>
@@ -3502,10 +3495,10 @@
         <v>13.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>114.8</v>
+        <v>71.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3514,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2078.2</v>
+        <v>207.8</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>118.4</v>
@@ -3530,55 +3523,55 @@
         <v>66.09999999999999</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>292.2</v>
+        <v>92.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>352.3</v>
+        <v>32.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>56.7</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>507.9</v>
+        <v>50.1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>18.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>101</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>59.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>380.9</v>
+        <v>3809.1</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>33.2</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>81.59999999999999</v>
@@ -3587,7 +3580,7 @@
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>429.8</v>
+        <v>429.5</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3609,7 +3602,7 @@
       <c r="D38" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="E38" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="F38" s="3" t="n">
@@ -3618,19 +3611,19 @@
       <c r="G38" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="H38" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="I38" s="8" t="n">
-        <v>17</v>
+      <c r="I38" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="M38" s="3" t="n">
@@ -3640,16 +3633,16 @@
         <v>15.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>8.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="8" t="n">
-        <v>97</v>
+      <c r="R38" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>17.6</v>
@@ -3666,11 +3659,11 @@
       <c r="W38" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="X38" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>3.1</v>
@@ -3695,7 +3688,7 @@
         <v>25.9</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.5</v>
@@ -3707,7 +3700,7 @@
         <v>7.6</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>5.3</v>
@@ -3715,29 +3708,29 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="8" t="n">
+      <c r="L39" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>24.8</v>
+        <v>25.8</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>26</v>
@@ -3745,11 +3738,11 @@
       <c r="U39" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="V39" s="8" t="n">
-        <v>71.5</v>
+      <c r="V39" s="3" t="n">
+        <v>21.5</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>16.5</v>
@@ -3780,22 +3773,22 @@
         <v>26</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="G40" s="8" t="n">
-        <v>65.3</v>
+      <c r="G40" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>15.3</v>
+        <v>5.3</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3813,7 +3806,7 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>25.4</v>
@@ -3822,10 +3815,10 @@
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>1948.8</v>
+        <v>48</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>16.7</v>
@@ -3865,7 +3858,7 @@
         <v>26.2</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>18.1</v>
@@ -3876,22 +3869,22 @@
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>18.8</v>
+        <v>10.7</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
@@ -3903,10 +3896,10 @@
         <v>17.2</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>8.1</v>
+        <v>22.1</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>947</v>
+        <v>47</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>17</v>
@@ -3917,11 +3910,11 @@
       <c r="W41" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="8" t="n">
-        <v>88.8</v>
+      <c r="X41" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>239</v>
+        <v>59</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>16.8</v>
@@ -3945,11 +3938,11 @@
       <c r="D42" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="8" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="F42" s="8" t="n">
-        <v>81.7</v>
+      <c r="E42" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>16.5</v>
@@ -3958,31 +3951,31 @@
         <v>5.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="M42" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="N42" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>18.2</v>
+        <v>98</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>26.7</v>
+        <v>26.1</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18.2</v>
@@ -3992,16 +3985,16 @@
         <v>49</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>14.4</v>
+        <v>17.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="8" t="n">
+      <c r="W42" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>61</v>
@@ -4031,7 +4024,7 @@
       <c r="E43" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="F43" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G43" s="3" t="n">
@@ -4044,22 +4037,22 @@
         <v>3.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>29.4</v>
+        <v>5.4</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N43" s="8" t="n">
-        <v>19.8</v>
+        <v>11.4</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>0.6</v>
@@ -4074,25 +4067,25 @@
         <v>46.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>22.8</v>
+        <v>32.2</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="V43" s="8" t="n">
-        <v>22.4</v>
+      <c r="V43" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="X43" s="8" t="n">
-        <v>120.9</v>
+      <c r="X43" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>239.2</v>
+        <v>29.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4159,34 +4152,34 @@
         <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>32.9</v>
+        <v>32.4</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>181.9</v>
+        <v>18.9</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>56.4</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>155.9</v>
+        <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>161.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>9498</v>
+        <v>26</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>126.3</v>
@@ -4195,10 +4188,10 @@
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>282.5</v>
+        <v>252.5</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>79.8</v>
@@ -4210,13 +4203,13 @@
         <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>10688.8</v>
+        <v>60.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>2302.8</v>
+        <v>302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>20.7</v>
+        <v>50.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4237,14 +4230,14 @@
       <c r="D46" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="8" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="F46" s="8" t="n">
+      <c r="E46" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F46" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>51.3</v>
+      <c r="G46" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.5</v>
@@ -4253,25 +4246,25 @@
         <v>3.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K46" s="8" t="n">
-        <v>1111.9</v>
-      </c>
-      <c r="L46" s="8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>25.3</v>
@@ -4280,25 +4273,25 @@
         <v>17.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>11.9</v>
+        <v>16.8</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="U46" s="8" t="n">
-        <v>65.40000000000001</v>
+      <c r="U46" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W46" s="8" t="n">
+        <v>218.4</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>161.2</v>
+        <v>61.2</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>10.1</v>
